--- a/artfynd/A 64829-2023 artfynd.xlsx
+++ b/artfynd/A 64829-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64829-2023 artfynd.xlsx
+++ b/artfynd/A 64829-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81041288</v>
+        <v>81041645</v>
       </c>
       <c r="B2" t="n">
-        <v>95524</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224365</v>
+        <v>167</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Riplummer</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. monostachyon</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Grev. &amp; Hook.) Selander</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Karesuando; 291,7°1,69km från Laestadius pörte, T lm</t>
+          <t>Karesuando begravningsplats; 34,1°417m från vägens passage över ”Saksajoki”, T lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>804167.1161778937</v>
+        <v>804098</v>
       </c>
       <c r="R2" t="n">
-        <v>7610936.766028451</v>
+        <v>7611570</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-07-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-07-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägkant mot myr</t>
+          <t>Vägkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,50 +777,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81042738</v>
+        <v>81041288</v>
       </c>
       <c r="B3" t="n">
-        <v>95591</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222112</v>
+        <v>224365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Riplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Lycopodium clavatum subsp. monostachyon</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(Grev. &amp; Hook.) Selander</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mertajärvi; 21,8°1,81km från södra vägskälet mot byn, T lm</t>
+          <t>Karesuando; 291,7°1,69km från Laestadius pörte, T lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>795941.4908107573</v>
+        <v>804167</v>
       </c>
       <c r="R3" t="n">
-        <v>7601002.062272297</v>
+        <v>7610937</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-08-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-07-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,7 +861,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Vältrampad gräsyta vid busshållplats</t>
+          <t>Vägkant mot myr</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -906,6 +876,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>81042738</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mertajärvi; 21,8°1,81km från södra vägskälet mot byn, T lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>795941</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7601002</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karesuando</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-08-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-08-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vältrampad gräsyta vid busshållplats</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ola Löfgren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ola Löfgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64829-2023 artfynd.xlsx
+++ b/artfynd/A 64829-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81041645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81041288</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,8 +993,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81042738</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>